--- a/NN/reports/model_design_experiments.xlsx
+++ b/NN/reports/model_design_experiments.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5323276875850096</v>
+        <v>0.5148302229643145</v>
       </c>
       <c r="D2" t="n">
-        <v>2.453655374956339</v>
+        <v>2.499134353654065</v>
       </c>
       <c r="E2" t="n">
-        <v>1.659992541271317</v>
+        <v>1.666081300833879</v>
       </c>
       <c r="F2" t="n">
-        <v>10.46658913664396</v>
+        <v>10.521003146699</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3627366039351571</v>
+        <v>0.3627366039351569</v>
       </c>
       <c r="D3" t="n">
         <v>2.864192621704481</v>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3627366039351569</v>
+        <v>0.3627366039351571</v>
       </c>
       <c r="D4" t="n">
         <v>2.864192621704481</v>
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5323276875850096</v>
+        <v>0.5148302229643145</v>
       </c>
       <c r="E2" t="n">
-        <v>2.453655374956339</v>
+        <v>2.499134353654065</v>
       </c>
       <c r="F2" t="n">
-        <v>1.659992541271317</v>
+        <v>1.666081300833879</v>
       </c>
       <c r="G2" t="n">
-        <v>10.46658913664396</v>
+        <v>10.521003146699</v>
       </c>
     </row>
     <row r="3">
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.3627366039351571</v>
+        <v>0.3627366039351569</v>
       </c>
       <c r="E3" t="n">
         <v>2.864192621704481</v>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3627366039351569</v>
+        <v>0.3627366039351571</v>
       </c>
       <c r="E4" t="n">
         <v>2.864192621704481</v>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D50"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1236,17 +1236,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -1256,17 +1256,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -1276,17 +1276,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -1296,17 +1296,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -1316,17 +1316,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -1336,17 +1336,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -1356,17 +1356,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -1376,17 +1376,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -1396,17 +1396,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="D27" t="b">
@@ -1416,17 +1416,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="D28" t="b">
@@ -1436,17 +1436,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -1456,17 +1456,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="D30" t="b">
@@ -1476,17 +1476,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -1496,17 +1496,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="D32" t="b">
@@ -1516,17 +1516,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -1536,340 +1536,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="D34" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>raw_sugar_color</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>raw_sugar_color</t>
-        </is>
-      </c>
-      <c r="D35" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>raw_syrup_brix</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>raw_syrup_brix</t>
-        </is>
-      </c>
-      <c r="D36" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>raw_syrup_color</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>raw_syrup_color</t>
-        </is>
-      </c>
-      <c r="D37" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="D38" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>lime_alkalinity</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>lime_alkalinity</t>
-        </is>
-      </c>
-      <c r="D39" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>co2_percent</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>co2_percent</t>
-        </is>
-      </c>
-      <c r="D40" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="D41" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>carbonated_pH</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>carbonated_pH</t>
-        </is>
-      </c>
-      <c r="D42" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>raw_sugar_color</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>raw_sugar_color</t>
-        </is>
-      </c>
-      <c r="D43" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>raw_syrup_brix</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>raw_syrup_brix</t>
-        </is>
-      </c>
-      <c r="D44" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>raw_syrup_color</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>raw_syrup_color</t>
-        </is>
-      </c>
-      <c r="D45" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="D46" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>lime_alkalinity</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>lime_alkalinity</t>
-        </is>
-      </c>
-      <c r="D47" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>co2_percent</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>co2_percent</t>
-        </is>
-      </c>
-      <c r="D48" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="D49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>carbonated_pH</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>carbonated_pH</t>
-        </is>
-      </c>
-      <c r="D50" t="b">
         <v>0</v>
       </c>
     </row>

--- a/NN/reports/model_design_experiments.xlsx
+++ b/NN/reports/model_design_experiments.xlsx
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3627366039351569</v>
+        <v>0.3627366039351571</v>
       </c>
       <c r="D3" t="n">
         <v>2.864192621704481</v>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.3627366039351569</v>
+        <v>0.3627366039351571</v>
       </c>
       <c r="E3" t="n">
         <v>2.864192621704481</v>

--- a/NN/reports/model_design_experiments.xlsx
+++ b/NN/reports/model_design_experiments.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -503,7 +503,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5148302229643145</v>
+        <v>0.3627366039351571</v>
       </c>
       <c r="D2" t="n">
-        <v>2.499134353654065</v>
+        <v>2.864192621704481</v>
       </c>
       <c r="E2" t="n">
-        <v>1.666081300833879</v>
+        <v>1.884821094216968</v>
       </c>
       <c r="F2" t="n">
-        <v>10.521003146699</v>
+        <v>11.56787509849947</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5148302229643145</v>
+        <v>0.3627366039351571</v>
       </c>
       <c r="E2" t="n">
-        <v>2.499134353654065</v>
+        <v>2.864192621704481</v>
       </c>
       <c r="F2" t="n">
-        <v>1.666081300833879</v>
+        <v>1.884821094216968</v>
       </c>
       <c r="G2" t="n">
-        <v>10.521003146699</v>
+        <v>11.56787509849947</v>
       </c>
     </row>
     <row r="3">
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1056,17 +1056,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>filtercake_moisture</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -1076,17 +1076,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>filtercake_sugar</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="D11" t="b">
@@ -1096,17 +1096,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>sweetwater_brix</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="D12" t="b">
@@ -1116,17 +1116,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="D13" t="b">
@@ -1136,17 +1136,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="D14" t="b">
@@ -1156,17 +1156,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>sulphited_color</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -1176,17 +1176,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="D16" t="b">
@@ -1196,17 +1196,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -1216,17 +1216,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A_FULL_LEAKY_BASELINE</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>standard_liquor_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="D18" t="b">
@@ -1236,17 +1236,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -1256,17 +1256,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -1276,17 +1276,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -1296,17 +1296,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -1316,17 +1316,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -1336,17 +1336,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -1356,200 +1356,20 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>C_NO_TIME</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="D25" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>carbonated_pH</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>carbonated_pH</t>
-        </is>
-      </c>
-      <c r="D26" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>raw_sugar_color</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>raw_sugar_color</t>
-        </is>
-      </c>
-      <c r="D27" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>raw_syrup_brix</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>raw_syrup_brix</t>
-        </is>
-      </c>
-      <c r="D28" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>raw_syrup_color</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>raw_syrup_color</t>
-        </is>
-      </c>
-      <c r="D29" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>lime_milk_baume</t>
-        </is>
-      </c>
-      <c r="D30" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>lime_alkalinity</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>lime_alkalinity</t>
-        </is>
-      </c>
-      <c r="D31" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>co2_percent</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>co2_percent</t>
-        </is>
-      </c>
-      <c r="D32" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>carbonated_alkalinity</t>
-        </is>
-      </c>
-      <c r="D33" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>C_NO_TIME</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>carbonated_pH</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>carbonated_pH</t>
-        </is>
-      </c>
-      <c r="D34" t="b">
         <v>0</v>
       </c>
     </row>

--- a/NN/reports/model_design_experiments.xlsx
+++ b/NN/reports/model_design_experiments.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -503,11 +503,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -541,11 +541,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -579,11 +579,11 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
     </row>
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3627366039351571</v>
+        <v>0.5817248891149778</v>
       </c>
       <c r="D2" t="n">
-        <v>2.864192621704481</v>
+        <v>0.2875234156253413</v>
       </c>
       <c r="E2" t="n">
-        <v>1.884821094216968</v>
+        <v>0.1756362523540489</v>
       </c>
       <c r="F2" t="n">
-        <v>11.56787509849947</v>
+        <v>13.91040792305623</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -677,16 +677,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3627366039351571</v>
+        <v>0.5817248891149778</v>
       </c>
       <c r="D3" t="n">
-        <v>2.864192621704481</v>
+        <v>0.2875234156253413</v>
       </c>
       <c r="E3" t="n">
-        <v>1.884821094216968</v>
+        <v>0.1756362523540489</v>
       </c>
       <c r="F3" t="n">
-        <v>11.56787509849947</v>
+        <v>13.91040792305623</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -704,16 +704,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.3627366039351571</v>
+        <v>0.5817248891149777</v>
       </c>
       <c r="D4" t="n">
-        <v>2.864192621704481</v>
+        <v>0.2875234156253413</v>
       </c>
       <c r="E4" t="n">
-        <v>1.884821094216968</v>
+        <v>0.1756362523540489</v>
       </c>
       <c r="F4" t="n">
-        <v>11.56787509849947</v>
+        <v>13.91040792305623</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -783,20 +783,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.3627366039351571</v>
+        <v>0.5817248891149778</v>
       </c>
       <c r="E2" t="n">
-        <v>2.864192621704481</v>
+        <v>0.2875234156253413</v>
       </c>
       <c r="F2" t="n">
-        <v>1.884821094216968</v>
+        <v>0.1756362523540489</v>
       </c>
       <c r="G2" t="n">
-        <v>11.56787509849947</v>
+        <v>13.91040792305623</v>
       </c>
     </row>
     <row r="3">
@@ -812,20 +812,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.3627366039351571</v>
+        <v>0.5817248891149778</v>
       </c>
       <c r="E3" t="n">
-        <v>2.864192621704481</v>
+        <v>0.2875234156253413</v>
       </c>
       <c r="F3" t="n">
-        <v>1.884821094216968</v>
+        <v>0.1756362523540489</v>
       </c>
       <c r="G3" t="n">
-        <v>11.56787509849947</v>
+        <v>13.91040792305623</v>
       </c>
     </row>
     <row r="4">
@@ -841,20 +841,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>white_total_points</t>
+          <t>work_period</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.3627366039351571</v>
+        <v>0.5817248891149777</v>
       </c>
       <c r="E4" t="n">
-        <v>2.864192621704481</v>
+        <v>0.2875234156253413</v>
       </c>
       <c r="F4" t="n">
-        <v>1.884821094216968</v>
+        <v>0.1756362523540489</v>
       </c>
       <c r="G4" t="n">
-        <v>11.56787509849947</v>
+        <v>13.91040792305623</v>
       </c>
     </row>
   </sheetData>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="D2" t="b">
@@ -921,12 +921,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="D3" t="b">
@@ -941,12 +941,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -961,12 +961,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -981,12 +981,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -1056,17 +1056,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -1076,17 +1076,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="D11" t="b">
@@ -1096,17 +1096,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="D12" t="b">
@@ -1116,17 +1116,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="D13" t="b">
@@ -1136,17 +1136,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="D14" t="b">
@@ -1156,17 +1156,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -1176,17 +1176,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="D16" t="b">
@@ -1196,17 +1196,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -1216,17 +1216,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C_NO_TIME</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>raw_sugar_color</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="D18" t="b">
@@ -1236,17 +1236,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C_NO_TIME</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -1256,17 +1256,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C_NO_TIME</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -1276,17 +1276,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>C_NO_TIME</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -1296,17 +1296,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>C_NO_TIME</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -1316,17 +1316,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>C_NO_TIME</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -1336,17 +1336,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>C_NO_TIME</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -1356,20 +1356,1160 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>C_NO_TIME</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="D25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A_FULL_LEAKY_BASELINE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="D26" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>A_FULL_LEAKY_BASELINE</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>A_FULL_LEAKY_BASELINE</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>raw_syrup_color</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>raw_syrup_color</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>carbonated_pH</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>carbonated_pH</t>
         </is>
       </c>
-      <c r="D25" t="b">
+      <c r="D35" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="D42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="D43" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="D44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="D47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="D48" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="D49" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="D50" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="D51" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="D52" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>B_CLEAN_PROCESS_MAIN</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="D55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>raw_syrup_brix</t>
+        </is>
+      </c>
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>raw_syrup_color</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>raw_syrup_color</t>
+        </is>
+      </c>
+      <c r="D57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>lime_milk_baume</t>
+        </is>
+      </c>
+      <c r="D58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>lime_alkalinity</t>
+        </is>
+      </c>
+      <c r="D59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>co2_percent</t>
+        </is>
+      </c>
+      <c r="D60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>carbonated_alkalinity</t>
+        </is>
+      </c>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>carbonated_pH</t>
+        </is>
+      </c>
+      <c r="D62" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>sulphited_pH</t>
+        </is>
+      </c>
+      <c r="D63" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>sulphited_brix</t>
+        </is>
+      </c>
+      <c r="D64" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>standard_liquor_pH</t>
+        </is>
+      </c>
+      <c r="D65" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>standard_liquor_brix</t>
+        </is>
+      </c>
+      <c r="D66" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>boiling_r1_pol</t>
+        </is>
+      </c>
+      <c r="D67" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>boiling_r1_q</t>
+        </is>
+      </c>
+      <c r="D68" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>boiling_r2_pol</t>
+        </is>
+      </c>
+      <c r="D69" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>boiling_r2_q</t>
+        </is>
+      </c>
+      <c r="D70" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>boiling_r3_pol</t>
+        </is>
+      </c>
+      <c r="D71" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>boiling_r3_q</t>
+        </is>
+      </c>
+      <c r="D72" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>wastewater_r1_pol</t>
+        </is>
+      </c>
+      <c r="D73" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>wastewater_r1_q</t>
+        </is>
+      </c>
+      <c r="D74" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>wastewater_r2_pol</t>
+        </is>
+      </c>
+      <c r="D75" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>wastewater_r2_q</t>
+        </is>
+      </c>
+      <c r="D76" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>wastewater_r3_pol</t>
+        </is>
+      </c>
+      <c r="D77" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>wastewater_r3_q</t>
+        </is>
+      </c>
+      <c r="D78" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="D79" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="D80" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="D81" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>boiler_tds</t>
+        </is>
+      </c>
+      <c r="D82" t="b">
         <v>0</v>
       </c>
     </row>

--- a/NN/reports/model_design_experiments.xlsx
+++ b/NN/reports/model_design_experiments.xlsx
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -503,11 +503,11 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -541,11 +541,11 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
     </row>
@@ -571,7 +571,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -579,11 +579,11 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
     </row>
@@ -650,16 +650,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.5817248891149778</v>
+        <v>0.4115470233332952</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2875234156253413</v>
+        <v>2.752318040842799</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1756362523540489</v>
+        <v>1.809449656460628</v>
       </c>
       <c r="F2" t="n">
-        <v>13.91040792305623</v>
+        <v>10.88782496077648</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -677,16 +677,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.5817248891149778</v>
+        <v>0.4115470233332952</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2875234156253413</v>
+        <v>2.752318040842799</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1756362523540489</v>
+        <v>1.809449656460628</v>
       </c>
       <c r="F3" t="n">
-        <v>13.91040792305623</v>
+        <v>10.88782496077648</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -704,16 +704,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.5817248891149777</v>
+        <v>0.4115470233332952</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2875234156253413</v>
+        <v>2.752318040842799</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1756362523540489</v>
+        <v>1.809449656460627</v>
       </c>
       <c r="F4" t="n">
-        <v>13.91040792305623</v>
+        <v>10.88782496077648</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -783,20 +783,20 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5817248891149778</v>
+        <v>0.4115470233332952</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2875234156253413</v>
+        <v>2.752318040842799</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1756362523540489</v>
+        <v>1.809449656460628</v>
       </c>
       <c r="G2" t="n">
-        <v>13.91040792305623</v>
+        <v>10.88782496077648</v>
       </c>
     </row>
     <row r="3">
@@ -812,20 +812,20 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.5817248891149778</v>
+        <v>0.4115470233332952</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2875234156253413</v>
+        <v>2.752318040842799</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1756362523540489</v>
+        <v>1.809449656460628</v>
       </c>
       <c r="G3" t="n">
-        <v>13.91040792305623</v>
+        <v>10.88782496077648</v>
       </c>
     </row>
     <row r="4">
@@ -841,20 +841,20 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>work_period</t>
+          <t>white_total_points</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5817248891149777</v>
+        <v>0.4115470233332952</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2875234156253413</v>
+        <v>2.752318040842799</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1756362523540489</v>
+        <v>1.809449656460627</v>
       </c>
       <c r="G4" t="n">
-        <v>13.91040792305623</v>
+        <v>10.88782496077648</v>
       </c>
     </row>
   </sheetData>
@@ -868,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D82"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -901,12 +901,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="D2" t="b">
@@ -921,12 +921,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="D3" t="b">
@@ -941,12 +941,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="D4" t="b">
@@ -961,12 +961,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="D5" t="b">
@@ -981,12 +981,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="D6" t="b">
@@ -1001,12 +1001,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="D7" t="b">
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="D8" t="b">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="D9" t="b">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="D10" t="b">
@@ -1081,12 +1081,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="D11" t="b">
@@ -1101,12 +1101,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="D12" t="b">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="D13" t="b">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="D14" t="b">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="D15" t="b">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="D16" t="b">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="D17" t="b">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="D18" t="b">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="D19" t="b">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="D20" t="b">
@@ -1281,12 +1281,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="D21" t="b">
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="D22" t="b">
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="D23" t="b">
@@ -1341,12 +1341,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="D24" t="b">
@@ -1361,12 +1361,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="D25" t="b">
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="D26" t="b">
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="D27" t="b">
@@ -1421,12 +1421,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="D28" t="b">
@@ -1436,17 +1436,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>B_CLEAN_PROCESS_MAIN</t>
+          <t>A_FULL_LEAKY_BASELINE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="D29" t="b">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="D30" t="b">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="D31" t="b">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="D32" t="b">
@@ -1521,12 +1521,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="D33" t="b">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="D34" t="b">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="D35" t="b">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="D36" t="b">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="D37" t="b">
@@ -1621,12 +1621,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="D38" t="b">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="D39" t="b">
@@ -1661,12 +1661,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="D40" t="b">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="D41" t="b">
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="D42" t="b">
@@ -1721,12 +1721,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="D43" t="b">
@@ -1741,12 +1741,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="D44" t="b">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="D45" t="b">
@@ -1781,12 +1781,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="D46" t="b">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="D47" t="b">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="D48" t="b">
@@ -1841,12 +1841,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="D49" t="b">
@@ -1861,12 +1861,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="D50" t="b">
@@ -1881,12 +1881,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="D51" t="b">
@@ -1901,12 +1901,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="D52" t="b">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="D53" t="b">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>boiler_pH</t>
         </is>
       </c>
       <c r="D54" t="b">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>boiler_tds</t>
+          <t>boiler_alkalinity</t>
         </is>
       </c>
       <c r="D55" t="b">
@@ -1976,17 +1976,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>C_NO_TIME</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>raw_syrup_brix</t>
+          <t>boiler_hardness</t>
         </is>
       </c>
       <c r="D56" t="b">
@@ -1996,17 +1996,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>C_NO_TIME</t>
+          <t>B_CLEAN_PROCESS_MAIN</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>raw_syrup_color</t>
+          <t>boiler_tds</t>
         </is>
       </c>
       <c r="D57" t="b">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>lime_milk_baume</t>
+          <t>raw_sugar_color</t>
         </is>
       </c>
       <c r="D58" t="b">
@@ -2041,12 +2041,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>lime_alkalinity</t>
+          <t>raw_syrup_brix</t>
         </is>
       </c>
       <c r="D59" t="b">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>co2_percent</t>
+          <t>raw_syrup_color</t>
         </is>
       </c>
       <c r="D60" t="b">
@@ -2081,12 +2081,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>carbonated_alkalinity</t>
+          <t>lime_milk_baume</t>
         </is>
       </c>
       <c r="D61" t="b">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>carbonated_pH</t>
+          <t>lime_alkalinity</t>
         </is>
       </c>
       <c r="D62" t="b">
@@ -2121,12 +2121,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>sulphited_pH</t>
+          <t>co2_percent</t>
         </is>
       </c>
       <c r="D63" t="b">
@@ -2141,12 +2141,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>sulphited_brix</t>
+          <t>carbonated_alkalinity</t>
         </is>
       </c>
       <c r="D64" t="b">
@@ -2161,12 +2161,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>standard_liquor_pH</t>
+          <t>carbonated_pH</t>
         </is>
       </c>
       <c r="D65" t="b">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>standard_liquor_brix</t>
+          <t>sulphited_pH</t>
         </is>
       </c>
       <c r="D66" t="b">
@@ -2201,12 +2201,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>boiling_r1_pol</t>
+          <t>sulphited_brix</t>
         </is>
       </c>
       <c r="D67" t="b">
@@ -2221,12 +2221,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>boiling_r1_q</t>
+          <t>standard_liquor_pH</t>
         </is>
       </c>
       <c r="D68" t="b">
@@ -2241,12 +2241,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>boiling_r2_pol</t>
+          <t>standard_liquor_brix</t>
         </is>
       </c>
       <c r="D69" t="b">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>boiling_r2_q</t>
+          <t>boiling_r1_pol</t>
         </is>
       </c>
       <c r="D70" t="b">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>boiling_r3_pol</t>
+          <t>boiling_r1_q</t>
         </is>
       </c>
       <c r="D71" t="b">
@@ -2301,12 +2301,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>boiling_r3_q</t>
+          <t>boiling_r2_pol</t>
         </is>
       </c>
       <c r="D72" t="b">
@@ -2321,12 +2321,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>wastewater_r1_pol</t>
+          <t>boiling_r2_q</t>
         </is>
       </c>
       <c r="D73" t="b">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>wastewater_r1_q</t>
+          <t>boiling_r3_pol</t>
         </is>
       </c>
       <c r="D74" t="b">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>wastewater_r2_pol</t>
+          <t>boiling_r3_q</t>
         </is>
       </c>
       <c r="D75" t="b">
@@ -2381,12 +2381,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>wastewater_r2_q</t>
+          <t>wastewater_r1_pol</t>
         </is>
       </c>
       <c r="D76" t="b">
@@ -2401,12 +2401,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>wastewater_r3_pol</t>
+          <t>wastewater_r1_q</t>
         </is>
       </c>
       <c r="D77" t="b">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>wastewater_r3_q</t>
+          <t>wastewater_r2_pol</t>
         </is>
       </c>
       <c r="D78" t="b">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>boiler_pH</t>
+          <t>wastewater_r2_q</t>
         </is>
       </c>
       <c r="D79" t="b">
@@ -2461,12 +2461,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>boiler_alkalinity</t>
+          <t>wastewater_r3_pol</t>
         </is>
       </c>
       <c r="D80" t="b">
@@ -2481,12 +2481,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>boiler_hardness</t>
+          <t>wastewater_r3_q</t>
         </is>
       </c>
       <c r="D81" t="b">
@@ -2501,15 +2501,75 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>boiler_pH</t>
+        </is>
+      </c>
+      <c r="D82" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>boiler_alkalinity</t>
+        </is>
+      </c>
+      <c r="D83" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>boiler_hardness</t>
+        </is>
+      </c>
+      <c r="D84" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>C_NO_TIME</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>boiler_tds</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>boiler_tds</t>
         </is>
       </c>
-      <c r="D82" t="b">
+      <c r="D85" t="b">
         <v>0</v>
       </c>
     </row>

--- a/NN/reports/model_design_experiments.xlsx
+++ b/NN/reports/model_design_experiments.xlsx
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4115470233332952</v>
+        <v>0.4115470233332953</v>
       </c>
       <c r="D2" t="n">
         <v>2.752318040842799</v>
       </c>
       <c r="E2" t="n">
-        <v>1.809449656460628</v>
+        <v>1.809449656460627</v>
       </c>
       <c r="F2" t="n">
         <v>10.88782496077648</v>
@@ -710,7 +710,7 @@
         <v>2.752318040842799</v>
       </c>
       <c r="E4" t="n">
-        <v>1.809449656460627</v>
+        <v>1.809449656460628</v>
       </c>
       <c r="F4" t="n">
         <v>10.88782496077648</v>
@@ -787,13 +787,13 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4115470233332952</v>
+        <v>0.4115470233332953</v>
       </c>
       <c r="E2" t="n">
         <v>2.752318040842799</v>
       </c>
       <c r="F2" t="n">
-        <v>1.809449656460628</v>
+        <v>1.809449656460627</v>
       </c>
       <c r="G2" t="n">
         <v>10.88782496077648</v>
@@ -851,7 +851,7 @@
         <v>2.752318040842799</v>
       </c>
       <c r="F4" t="n">
-        <v>1.809449656460627</v>
+        <v>1.809449656460628</v>
       </c>
       <c r="G4" t="n">
         <v>10.88782496077648</v>

--- a/NN/reports/model_design_experiments.xlsx
+++ b/NN/reports/model_design_experiments.xlsx
@@ -656,7 +656,7 @@
         <v>2.752318040842799</v>
       </c>
       <c r="E2" t="n">
-        <v>1.809449656460627</v>
+        <v>1.809449656460628</v>
       </c>
       <c r="F2" t="n">
         <v>10.88782496077648</v>
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.4115470233332952</v>
+        <v>0.4115470233332953</v>
       </c>
       <c r="D3" t="n">
         <v>2.752318040842799</v>
@@ -793,7 +793,7 @@
         <v>2.752318040842799</v>
       </c>
       <c r="F2" t="n">
-        <v>1.809449656460627</v>
+        <v>1.809449656460628</v>
       </c>
       <c r="G2" t="n">
         <v>10.88782496077648</v>
@@ -816,7 +816,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4115470233332952</v>
+        <v>0.4115470233332953</v>
       </c>
       <c r="E3" t="n">
         <v>2.752318040842799</v>

--- a/NN/reports/model_design_experiments.xlsx
+++ b/NN/reports/model_design_experiments.xlsx
@@ -650,7 +650,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.4115470233332953</v>
+        <v>0.4115470233332952</v>
       </c>
       <c r="D2" t="n">
         <v>2.752318040842799</v>
@@ -683,7 +683,7 @@
         <v>2.752318040842799</v>
       </c>
       <c r="E3" t="n">
-        <v>1.809449656460628</v>
+        <v>1.809449656460627</v>
       </c>
       <c r="F3" t="n">
         <v>10.88782496077648</v>
@@ -787,7 +787,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.4115470233332953</v>
+        <v>0.4115470233332952</v>
       </c>
       <c r="E2" t="n">
         <v>2.752318040842799</v>
@@ -822,7 +822,7 @@
         <v>2.752318040842799</v>
       </c>
       <c r="F3" t="n">
-        <v>1.809449656460628</v>
+        <v>1.809449656460627</v>
       </c>
       <c r="G3" t="n">
         <v>10.88782496077648</v>
